--- a/data/trans_bre/P44D-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P44D-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>-3,08%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 46,36</t>
+          <t>-36,37; 44,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 53,27</t>
+          <t>-24,87; 50,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 10,0</t>
+          <t>-9,96; 8,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-64,53; 319,61</t>
+          <t>-76,28; 255,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,5; 266,93</t>
+          <t>-56,68; 232,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,78; 56,05</t>
+          <t>-38,36; 49,15</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-1,82</t>
+          <t>-3,89</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-10,66%</t>
+          <t>-21,58%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 52,84</t>
+          <t>-44,0; 56,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,05; 54,89</t>
+          <t>-41,56; 61,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 8,53</t>
+          <t>-14,12; 6,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 322,74</t>
+          <t>-100,0; 457,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 317,28</t>
+          <t>-100,0; 336,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,46; 68,49</t>
+          <t>-59,25; 50,52</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>146,33%</t>
+          <t>-11,81%</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,76; 75,96</t>
+          <t>4,94; 72,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-27,79; -3,09</t>
+          <t>-26,9; -2,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 15,62</t>
+          <t>-7,64; 7,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-73,36; 3332,6</t>
+          <t>-81,75; 278,17</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>119,45%</t>
+          <t>138,28%</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 19,07</t>
+          <t>-6,52; 21,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 6,87</t>
+          <t>-0,85; 7,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,42; 929,57</t>
+          <t>-55,44; 844,81</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,66</t>
+          <t>0,0; 33,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,28</t>
+          <t>4,12</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,54</t>
+          <t>2,16; 7,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>-25,55%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 16,37</t>
+          <t>-6,0; 14,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 5,59</t>
+          <t>-11,03; 5,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 5,72</t>
+          <t>-5,39; 0,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 240,15</t>
+          <t>-36,44; 198,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-62,46; 55,04</t>
+          <t>-62,41; 60,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 174,06</t>
+          <t>-47,16; 5,47</t>
         </is>
       </c>
     </row>
